--- a/diseases/d109/2000-2004.xlsx
+++ b/diseases/d109/2000-2004.xlsx
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -21153,7 +21153,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -22180,7 +22180,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -23207,7 +23207,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -25261,7 +25261,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -26288,7 +26288,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -28342,7 +28342,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -29369,7 +29369,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -30396,7 +30396,7 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -31423,7 +31423,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -32450,7 +32450,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -33477,7 +33477,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -34504,7 +34504,7 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -35531,7 +35531,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -36558,7 +36558,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -37585,7 +37585,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -38612,7 +38612,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -39639,7 +39639,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -40666,7 +40666,7 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -41693,7 +41693,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -42720,7 +42720,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -43747,7 +43747,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -44774,7 +44774,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -45801,7 +45801,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -46828,7 +46828,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -47855,7 +47855,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -49909,7 +49909,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -50936,7 +50936,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -51963,7 +51963,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -52990,7 +52990,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -54017,7 +54017,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -55044,7 +55044,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -56071,7 +56071,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -57098,7 +57098,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -58125,7 +58125,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -59152,7 +59152,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -60179,7 +60179,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -61206,7 +61206,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -62233,7 +62233,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">

--- a/diseases/d109/2000-2004.xlsx
+++ b/diseases/d109/2000-2004.xlsx
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -21153,7 +21153,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -22180,7 +22180,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -23207,7 +23207,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -25261,7 +25261,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -26288,7 +26288,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -28342,7 +28342,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -29369,7 +29369,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -30396,7 +30396,7 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -31423,7 +31423,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -32450,7 +32450,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -33477,7 +33477,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -34504,7 +34504,7 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -35531,7 +35531,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -36558,7 +36558,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -37585,7 +37585,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -38612,7 +38612,7 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN186" t="b">
@@ -39639,7 +39639,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -40666,7 +40666,7 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -41693,7 +41693,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -42720,7 +42720,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -43747,7 +43747,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -44774,7 +44774,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -45801,7 +45801,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -46828,7 +46828,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -47855,7 +47855,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -48882,7 +48882,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -49909,7 +49909,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -50936,7 +50936,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -51963,7 +51963,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -52990,7 +52990,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -54017,7 +54017,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -55044,7 +55044,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -56071,7 +56071,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -57098,7 +57098,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -58125,7 +58125,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -59152,7 +59152,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -60179,7 +60179,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -61206,7 +61206,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -62233,7 +62233,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
